--- a/data/intermediate/remesas.xlsx
+++ b/data/intermediate/remesas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="381">
   <si>
     <t>fecha</t>
   </si>
@@ -1154,6 +1154,9 @@
   </si>
   <si>
     <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2026-07-01</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B379"/>
+  <dimension ref="A1:B380"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1501,7 +1504,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>286.525544</v>
+        <v>286.526449</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1509,7 +1512,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>294.929325</v>
+        <v>294.928848</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1517,7 +1520,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>286.017378</v>
+        <v>286.018613</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1525,7 +1528,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>300.38636</v>
+        <v>300.383655</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1533,7 +1536,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>299.013398</v>
+        <v>299.013286</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1541,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>317.155143</v>
+        <v>317.155283</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1549,7 +1552,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>323.632964</v>
+        <v>323.630495</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1557,7 +1560,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>331.115815</v>
+        <v>331.116287</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1565,7 +1568,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>318.522617</v>
+        <v>318.521278</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1573,7 +1576,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>330.768686</v>
+        <v>330.767129</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1581,7 +1584,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>289.985323</v>
+        <v>289.985341</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1589,7 +1592,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>288.993686</v>
+        <v>288.999019</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1597,7 +1600,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>349.156587</v>
+        <v>349.158644</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1605,7 +1608,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>322.260993</v>
+        <v>322.260688</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1613,7 +1616,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>343.164863</v>
+        <v>343.163678</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1621,7 +1624,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>387.676274</v>
+        <v>387.675553</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1629,7 +1632,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>345.169702</v>
+        <v>345.169822</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1637,7 +1640,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>336.552094</v>
+        <v>336.549753</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1645,7 +1648,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>346.189833</v>
+        <v>346.189648</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1653,7 +1656,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>357.24109</v>
+        <v>357.240343</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1661,7 +1664,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>343.906577</v>
+        <v>343.904971</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1669,7 +1672,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>352.61526</v>
+        <v>352.614883</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1677,7 +1680,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>359.256174</v>
+        <v>359.255251</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1685,7 +1688,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>367.92104</v>
+        <v>367.929574</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1693,7 +1696,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>376.443356</v>
+        <v>376.445239</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1701,7 +1704,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>393.332528</v>
+        <v>393.33151</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1709,7 +1712,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>403.167426</v>
+        <v>403.163499</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1717,7 +1720,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>405.421516</v>
+        <v>405.422916</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1725,7 +1728,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>410.4544</v>
+        <v>410.453313</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1733,7 +1736,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>416.646328</v>
+        <v>416.64475</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1741,7 +1744,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>411.239339</v>
+        <v>411.239081</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1749,7 +1752,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>402.26774</v>
+        <v>402.265496</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1757,7 +1760,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>431.797394</v>
+        <v>431.796803</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1765,7 +1768,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>428.67883</v>
+        <v>428.678596</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1773,7 +1776,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>390.581141</v>
+        <v>390.579262</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1781,7 +1784,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>384.526479</v>
+        <v>384.536854</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1789,7 +1792,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>427.929636</v>
+        <v>427.929663</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1797,7 +1800,7 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>431.821182</v>
+        <v>431.819984</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1805,7 +1808,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>430.94142</v>
+        <v>430.940776</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1813,7 +1816,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>436.330922</v>
+        <v>436.330094</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1821,7 +1824,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>445.133601</v>
+        <v>445.131033</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1829,7 +1832,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>463.032366</v>
+        <v>463.032026</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1837,7 +1840,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>462.712421</v>
+        <v>462.71223</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1845,7 +1848,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>459.257867</v>
+        <v>459.255165</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1853,7 +1856,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>474.252769</v>
+        <v>474.252274</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1861,7 +1864,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>468.198373</v>
+        <v>468.196934</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1869,7 +1872,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>512.4834499999999</v>
+        <v>512.483112</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1877,7 +1880,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>614.5761670000001</v>
+        <v>614.591907</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1885,7 +1888,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>448.287046</v>
+        <v>448.285173</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1893,7 +1896,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>454.877465</v>
+        <v>454.876267</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1901,7 +1904,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>465.052112</v>
+        <v>465.053031</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1909,7 +1912,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>467.281326</v>
+        <v>467.280617</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1917,7 +1920,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>493.017585</v>
+        <v>493.014814</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1925,7 +1928,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>485.362283</v>
+        <v>485.361954</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1933,7 +1936,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>481.600805</v>
+        <v>481.598959</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1941,7 +1944,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>499.953742</v>
+        <v>499.95223</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1949,7 +1952,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>484.850791</v>
+        <v>484.850259</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1957,7 +1960,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>494.036421</v>
+        <v>494.032813</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1965,7 +1968,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>547.526742</v>
+        <v>547.529221</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1973,7 +1976,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>581.088558</v>
+        <v>581.103494</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1981,7 +1984,7 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>508.496809</v>
+        <v>508.494024</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1989,7 +1992,7 @@
         <v>63</v>
       </c>
       <c r="B63">
-        <v>500.332538</v>
+        <v>500.331763</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1997,7 +2000,7 @@
         <v>64</v>
       </c>
       <c r="B64">
-        <v>496.276839</v>
+        <v>496.277866</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2005,7 +2008,7 @@
         <v>65</v>
       </c>
       <c r="B65">
-        <v>509.2841</v>
+        <v>509.279881</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2013,7 +2016,7 @@
         <v>66</v>
       </c>
       <c r="B66">
-        <v>504.762201</v>
+        <v>504.762869</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2021,7 +2024,7 @@
         <v>67</v>
       </c>
       <c r="B67">
-        <v>506.986321</v>
+        <v>506.986156</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2029,7 +2032,7 @@
         <v>68</v>
       </c>
       <c r="B68">
-        <v>537.1797309999999</v>
+        <v>537.175924</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2037,7 +2040,7 @@
         <v>69</v>
       </c>
       <c r="B69">
-        <v>566.861509</v>
+        <v>566.861506</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2045,7 +2048,7 @@
         <v>70</v>
       </c>
       <c r="B70">
-        <v>564.398499</v>
+        <v>564.395993</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2053,7 +2056,7 @@
         <v>71</v>
       </c>
       <c r="B71">
-        <v>572.158455</v>
+        <v>572.15602</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2061,7 +2064,7 @@
         <v>72</v>
       </c>
       <c r="B72">
-        <v>633.418869</v>
+        <v>633.422703</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2069,7 +2072,7 @@
         <v>73</v>
       </c>
       <c r="B73">
-        <v>671.148739</v>
+        <v>671.159734</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2077,7 +2080,7 @@
         <v>74</v>
       </c>
       <c r="B74">
-        <v>712.936988</v>
+        <v>712.938267</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2085,7 +2088,7 @@
         <v>75</v>
       </c>
       <c r="B75">
-        <v>741.54921</v>
+        <v>741.547317</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2093,7 +2096,7 @@
         <v>76</v>
       </c>
       <c r="B76">
-        <v>728.849767</v>
+        <v>728.849157</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2101,7 +2104,7 @@
         <v>77</v>
       </c>
       <c r="B77">
-        <v>743.133456</v>
+        <v>743.130152</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2109,7 +2112,7 @@
         <v>78</v>
       </c>
       <c r="B78">
-        <v>688.983477</v>
+        <v>688.984183</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2117,7 +2120,7 @@
         <v>79</v>
       </c>
       <c r="B79">
-        <v>708.905705</v>
+        <v>708.903452</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2125,7 +2128,7 @@
         <v>80</v>
       </c>
       <c r="B80">
-        <v>759.564095</v>
+        <v>759.561597</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2133,7 +2136,7 @@
         <v>81</v>
       </c>
       <c r="B81">
-        <v>732.2867639999999</v>
+        <v>732.286267</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -2141,7 +2144,7 @@
         <v>82</v>
       </c>
       <c r="B82">
-        <v>771.753657</v>
+        <v>771.747714</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -2149,7 +2152,7 @@
         <v>83</v>
       </c>
       <c r="B83">
-        <v>797.683354</v>
+        <v>797.682984</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2157,7 +2160,7 @@
         <v>84</v>
       </c>
       <c r="B84">
-        <v>752.8143240000001</v>
+        <v>752.819994</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2165,7 +2168,7 @@
         <v>85</v>
       </c>
       <c r="B85">
-        <v>766.592794</v>
+        <v>766.602685</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2173,7 +2176,7 @@
         <v>86</v>
       </c>
       <c r="B86">
-        <v>778.7774470000001</v>
+        <v>778.779187</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2181,7 +2184,7 @@
         <v>87</v>
       </c>
       <c r="B87">
-        <v>837.530306</v>
+        <v>837.52849</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2189,7 +2192,7 @@
         <v>88</v>
       </c>
       <c r="B88">
-        <v>789.817196</v>
+        <v>789.81025</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2197,7 +2200,7 @@
         <v>89</v>
       </c>
       <c r="B89">
-        <v>777.5734650000001</v>
+        <v>777.5766640000001</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2205,7 +2208,7 @@
         <v>90</v>
       </c>
       <c r="B90">
-        <v>791.139233</v>
+        <v>791.1400190000001</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2213,7 +2216,7 @@
         <v>91</v>
       </c>
       <c r="B91">
-        <v>822.064768</v>
+        <v>822.059454</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -2221,7 +2224,7 @@
         <v>92</v>
       </c>
       <c r="B92">
-        <v>795.3431880000001</v>
+        <v>795.343473</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2229,7 +2232,7 @@
         <v>93</v>
       </c>
       <c r="B93">
-        <v>791.285085</v>
+        <v>791.28139</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -2237,7 +2240,7 @@
         <v>94</v>
       </c>
       <c r="B94">
-        <v>848.836693</v>
+        <v>848.83336</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -2245,7 +2248,7 @@
         <v>95</v>
       </c>
       <c r="B95">
-        <v>845.929333</v>
+        <v>845.932087</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2253,7 +2256,7 @@
         <v>96</v>
       </c>
       <c r="B96">
-        <v>812.8844319999999</v>
+        <v>812.8872229999999</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2261,7 +2264,7 @@
         <v>97</v>
       </c>
       <c r="B97">
-        <v>929.488618</v>
+        <v>929.4992549999999</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2269,7 +2272,7 @@
         <v>98</v>
       </c>
       <c r="B98">
-        <v>1167.552323</v>
+        <v>1167.555992</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2277,7 +2280,7 @@
         <v>99</v>
       </c>
       <c r="B99">
-        <v>1145.296767</v>
+        <v>1145.294891</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2285,7 +2288,7 @@
         <v>100</v>
       </c>
       <c r="B100">
-        <v>1159.173342</v>
+        <v>1159.170272</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2293,7 +2296,7 @@
         <v>101</v>
       </c>
       <c r="B101">
-        <v>1205.212875</v>
+        <v>1205.211172</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -2301,7 +2304,7 @@
         <v>102</v>
       </c>
       <c r="B102">
-        <v>1181.969946</v>
+        <v>1181.96701</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -2309,7 +2312,7 @@
         <v>103</v>
       </c>
       <c r="B103">
-        <v>1267.569046</v>
+        <v>1267.565074</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -2317,7 +2320,7 @@
         <v>104</v>
       </c>
       <c r="B104">
-        <v>1285.368368</v>
+        <v>1285.369174</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -2325,7 +2328,7 @@
         <v>105</v>
       </c>
       <c r="B105">
-        <v>1309.966046</v>
+        <v>1309.954451</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -2333,7 +2336,7 @@
         <v>106</v>
       </c>
       <c r="B106">
-        <v>1332.088363</v>
+        <v>1332.087127</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -2341,7 +2344,7 @@
         <v>107</v>
       </c>
       <c r="B107">
-        <v>1380.115626</v>
+        <v>1380.126714</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -2349,7 +2352,7 @@
         <v>108</v>
       </c>
       <c r="B108">
-        <v>1331.238706</v>
+        <v>1331.237008</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -2357,7 +2360,7 @@
         <v>109</v>
       </c>
       <c r="B109">
-        <v>1360.609491</v>
+        <v>1360.62695</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -2365,7 +2368,7 @@
         <v>110</v>
       </c>
       <c r="B110">
-        <v>1236.600364</v>
+        <v>1236.600019</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -2373,7 +2376,7 @@
         <v>111</v>
       </c>
       <c r="B111">
-        <v>1335.348078</v>
+        <v>1335.342366</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -2381,7 +2384,7 @@
         <v>112</v>
       </c>
       <c r="B112">
-        <v>1465.800993</v>
+        <v>1465.806539</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -2389,7 +2392,7 @@
         <v>113</v>
       </c>
       <c r="B113">
-        <v>1516.735383</v>
+        <v>1516.733334</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -2397,7 +2400,7 @@
         <v>114</v>
       </c>
       <c r="B114">
-        <v>1559.388347</v>
+        <v>1559.378564</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -2405,7 +2408,7 @@
         <v>115</v>
       </c>
       <c r="B115">
-        <v>1555.127995</v>
+        <v>1555.127655</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -2413,7 +2416,7 @@
         <v>116</v>
       </c>
       <c r="B116">
-        <v>1577.145765</v>
+        <v>1577.141144</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -2421,7 +2424,7 @@
         <v>117</v>
       </c>
       <c r="B117">
-        <v>1638.316293</v>
+        <v>1638.307348</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -2429,7 +2432,7 @@
         <v>118</v>
       </c>
       <c r="B118">
-        <v>1551.774326</v>
+        <v>1551.772954</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -2437,7 +2440,7 @@
         <v>119</v>
       </c>
       <c r="B119">
-        <v>1542.43449</v>
+        <v>1542.44689</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -2445,7 +2448,7 @@
         <v>120</v>
       </c>
       <c r="B120">
-        <v>1626.637405</v>
+        <v>1626.643586</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -2453,7 +2456,7 @@
         <v>121</v>
       </c>
       <c r="B121">
-        <v>1613.163508</v>
+        <v>1613.178401</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -2461,7 +2464,7 @@
         <v>122</v>
       </c>
       <c r="B122">
-        <v>1612.99212</v>
+        <v>1612.986173</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -2469,7 +2472,7 @@
         <v>123</v>
       </c>
       <c r="B123">
-        <v>1674.040615</v>
+        <v>1674.037275</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -2477,7 +2480,7 @@
         <v>124</v>
       </c>
       <c r="B124">
-        <v>1722.692932</v>
+        <v>1722.688886</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -2485,7 +2488,7 @@
         <v>125</v>
       </c>
       <c r="B125">
-        <v>1708.335763</v>
+        <v>1708.337165</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -2493,7 +2496,7 @@
         <v>126</v>
       </c>
       <c r="B126">
-        <v>1784.635865</v>
+        <v>1784.63018</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -2501,7 +2504,7 @@
         <v>127</v>
       </c>
       <c r="B127">
-        <v>1768.442525</v>
+        <v>1768.440934</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2509,7 +2512,7 @@
         <v>128</v>
       </c>
       <c r="B128">
-        <v>1769.15456</v>
+        <v>1769.142864</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2517,7 +2520,7 @@
         <v>129</v>
       </c>
       <c r="B129">
-        <v>1859.15129</v>
+        <v>1859.14707</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2525,7 +2528,7 @@
         <v>130</v>
       </c>
       <c r="B130">
-        <v>1847.487677</v>
+        <v>1847.485961</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2533,7 +2536,7 @@
         <v>131</v>
       </c>
       <c r="B131">
-        <v>1875.574824</v>
+        <v>1875.605797</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2541,7 +2544,7 @@
         <v>132</v>
       </c>
       <c r="B132">
-        <v>2036.917706</v>
+        <v>2036.92063</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2549,7 +2552,7 @@
         <v>133</v>
       </c>
       <c r="B133">
-        <v>2045.218413</v>
+        <v>2045.222304</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2557,7 +2560,7 @@
         <v>134</v>
       </c>
       <c r="B134">
-        <v>2088.476532</v>
+        <v>2088.475757</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -2565,7 +2568,7 @@
         <v>135</v>
       </c>
       <c r="B135">
-        <v>2124.387017</v>
+        <v>2124.382669</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -2573,7 +2576,7 @@
         <v>136</v>
       </c>
       <c r="B136">
-        <v>2081.222143</v>
+        <v>2081.22728</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -2581,7 +2584,7 @@
         <v>137</v>
       </c>
       <c r="B137">
-        <v>2115.425441</v>
+        <v>2115.408302</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -2589,7 +2592,7 @@
         <v>138</v>
       </c>
       <c r="B138">
-        <v>2172.062803</v>
+        <v>2172.062231</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -2597,7 +2600,7 @@
         <v>139</v>
       </c>
       <c r="B139">
-        <v>2151.566814</v>
+        <v>2151.564151</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -2605,7 +2608,7 @@
         <v>140</v>
       </c>
       <c r="B140">
-        <v>2099.59099</v>
+        <v>2099.575992</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -2613,7 +2616,7 @@
         <v>141</v>
       </c>
       <c r="B141">
-        <v>2111.681565</v>
+        <v>2111.677998</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -2621,7 +2624,7 @@
         <v>142</v>
       </c>
       <c r="B142">
-        <v>2117.610806</v>
+        <v>2117.602075</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -2629,7 +2632,7 @@
         <v>143</v>
       </c>
       <c r="B143">
-        <v>2302.463931</v>
+        <v>2302.524002</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -2637,7 +2640,7 @@
         <v>144</v>
       </c>
       <c r="B144">
-        <v>2126.396198</v>
+        <v>2126.39538</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -2645,7 +2648,7 @@
         <v>145</v>
       </c>
       <c r="B145">
-        <v>2103.191316</v>
+        <v>2103.18055</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -2653,7 +2656,7 @@
         <v>146</v>
       </c>
       <c r="B146">
-        <v>2239.022481</v>
+        <v>2239.028797</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -2661,7 +2664,7 @@
         <v>147</v>
       </c>
       <c r="B147">
-        <v>2144.697571</v>
+        <v>2144.693619</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -2669,7 +2672,7 @@
         <v>148</v>
       </c>
       <c r="B148">
-        <v>2096.064731</v>
+        <v>2096.062631</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -2677,7 +2680,7 @@
         <v>149</v>
       </c>
       <c r="B149">
-        <v>2185.674828</v>
+        <v>2185.665575</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -2685,7 +2688,7 @@
         <v>150</v>
       </c>
       <c r="B150">
-        <v>2122.862563</v>
+        <v>2122.858558</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -2693,7 +2696,7 @@
         <v>151</v>
       </c>
       <c r="B151">
-        <v>2135.51225</v>
+        <v>2135.503325</v>
       </c>
     </row>
     <row r="152" spans="1:2">
@@ -2701,7 +2704,7 @@
         <v>152</v>
       </c>
       <c r="B152">
-        <v>2337.483285</v>
+        <v>2337.474966</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -2709,7 +2712,7 @@
         <v>153</v>
       </c>
       <c r="B153">
-        <v>2290.543921</v>
+        <v>2290.543329</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -2717,7 +2720,7 @@
         <v>154</v>
       </c>
       <c r="B154">
-        <v>2280.302449</v>
+        <v>2280.283612</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -2725,7 +2728,7 @@
         <v>155</v>
       </c>
       <c r="B155">
-        <v>2424.296903</v>
+        <v>2424.371239</v>
       </c>
     </row>
     <row r="156" spans="1:2">
@@ -2733,7 +2736,7 @@
         <v>156</v>
       </c>
       <c r="B156">
-        <v>2232.257737</v>
+        <v>2232.256531</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -2741,7 +2744,7 @@
         <v>157</v>
       </c>
       <c r="B157">
-        <v>2244.995813</v>
+        <v>2244.982651</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -2749,7 +2752,7 @@
         <v>158</v>
       </c>
       <c r="B158">
-        <v>2159.872143</v>
+        <v>2159.877654</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -2757,7 +2760,7 @@
         <v>159</v>
       </c>
       <c r="B159">
-        <v>2136.064831</v>
+        <v>2136.063466</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -2765,7 +2768,7 @@
         <v>160</v>
       </c>
       <c r="B160">
-        <v>2173.896368</v>
+        <v>2173.873889</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -2773,7 +2776,7 @@
         <v>161</v>
       </c>
       <c r="B161">
-        <v>2185.224392</v>
+        <v>2185.235951</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -2781,7 +2784,7 @@
         <v>162</v>
       </c>
       <c r="B162">
-        <v>2146.595558</v>
+        <v>2146.581196</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -2789,7 +2792,7 @@
         <v>163</v>
       </c>
       <c r="B163">
-        <v>2199.98869</v>
+        <v>2199.981421</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -2797,7 +2800,7 @@
         <v>164</v>
       </c>
       <c r="B164">
-        <v>2136.18382</v>
+        <v>2136.184732</v>
       </c>
     </row>
     <row r="165" spans="1:2">
@@ -2805,7 +2808,7 @@
         <v>165</v>
       </c>
       <c r="B165">
-        <v>2053.752572</v>
+        <v>2053.741642</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -2813,7 +2816,7 @@
         <v>166</v>
       </c>
       <c r="B166">
-        <v>2158.27196</v>
+        <v>2158.269029</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -2821,7 +2824,7 @@
         <v>167</v>
       </c>
       <c r="B167">
-        <v>2716.008261</v>
+        <v>2716.080929</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -2829,7 +2832,7 @@
         <v>168</v>
       </c>
       <c r="B168">
-        <v>2057.027645</v>
+        <v>2057.013751</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -2837,7 +2840,7 @@
         <v>169</v>
       </c>
       <c r="B169">
-        <v>1994.622543</v>
+        <v>1994.625074</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -2845,7 +2848,7 @@
         <v>170</v>
       </c>
       <c r="B170">
-        <v>2044.215764</v>
+        <v>2044.21443</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -2853,7 +2856,7 @@
         <v>171</v>
       </c>
       <c r="B171">
-        <v>2141.503201</v>
+        <v>2141.500334</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -2861,7 +2864,7 @@
         <v>172</v>
       </c>
       <c r="B172">
-        <v>2028.222085</v>
+        <v>2028.219706</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -2869,7 +2872,7 @@
         <v>173</v>
       </c>
       <c r="B173">
-        <v>1841.734795</v>
+        <v>1841.735164</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -2877,7 +2880,7 @@
         <v>174</v>
       </c>
       <c r="B174">
-        <v>1737.615984</v>
+        <v>1737.597518</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -2885,7 +2888,7 @@
         <v>175</v>
       </c>
       <c r="B175">
-        <v>1844.812508</v>
+        <v>1844.81479</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -2893,7 +2896,7 @@
         <v>176</v>
       </c>
       <c r="B176">
-        <v>1810.392707</v>
+        <v>1810.395979</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -2901,7 +2904,7 @@
         <v>177</v>
       </c>
       <c r="B177">
-        <v>1751.024565</v>
+        <v>1751.017919</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -2909,7 +2912,7 @@
         <v>178</v>
       </c>
       <c r="B178">
-        <v>1776.916147</v>
+        <v>1776.910697</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -2917,7 +2920,7 @@
         <v>179</v>
       </c>
       <c r="B179">
-        <v>1757.511221</v>
+        <v>1757.543424</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -2925,7 +2928,7 @@
         <v>180</v>
       </c>
       <c r="B180">
-        <v>1737.614478</v>
+        <v>1737.610635</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -2933,7 +2936,7 @@
         <v>181</v>
       </c>
       <c r="B181">
-        <v>1744.437261</v>
+        <v>1744.439948</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -2941,7 +2944,7 @@
         <v>182</v>
       </c>
       <c r="B182">
-        <v>1741.578129</v>
+        <v>1741.571819</v>
       </c>
     </row>
     <row r="183" spans="1:2">
@@ -2949,7 +2952,7 @@
         <v>183</v>
       </c>
       <c r="B183">
-        <v>1806.511449</v>
+        <v>1806.509967</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -2957,7 +2960,7 @@
         <v>184</v>
       </c>
       <c r="B184">
-        <v>1823.994593</v>
+        <v>1823.999804</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -2965,7 +2968,7 @@
         <v>185</v>
       </c>
       <c r="B185">
-        <v>1812.4761</v>
+        <v>1812.476488</v>
       </c>
     </row>
     <row r="186" spans="1:2">
@@ -2973,7 +2976,7 @@
         <v>186</v>
       </c>
       <c r="B186">
-        <v>1936.770841</v>
+        <v>1936.751959</v>
       </c>
     </row>
     <row r="187" spans="1:2">
@@ -2981,7 +2984,7 @@
         <v>187</v>
       </c>
       <c r="B187">
-        <v>1792.676247</v>
+        <v>1792.68012</v>
       </c>
     </row>
     <row r="188" spans="1:2">
@@ -2989,7 +2992,7 @@
         <v>188</v>
       </c>
       <c r="B188">
-        <v>1867.518847</v>
+        <v>1867.518179</v>
       </c>
     </row>
     <row r="189" spans="1:2">
@@ -2997,7 +3000,7 @@
         <v>189</v>
       </c>
       <c r="B189">
-        <v>1889.511452</v>
+        <v>1889.512699</v>
       </c>
     </row>
     <row r="190" spans="1:2">
@@ -3005,7 +3008,7 @@
         <v>190</v>
       </c>
       <c r="B190">
-        <v>1760.396809</v>
+        <v>1760.389944</v>
       </c>
     </row>
     <row r="191" spans="1:2">
@@ -3013,7 +3016,7 @@
         <v>191</v>
       </c>
       <c r="B191">
-        <v>1817.050743</v>
+        <v>1817.06516</v>
       </c>
     </row>
     <row r="192" spans="1:2">
@@ -3021,7 +3024,7 @@
         <v>192</v>
       </c>
       <c r="B192">
-        <v>1839.906829</v>
+        <v>1839.9109</v>
       </c>
     </row>
     <row r="193" spans="1:2">
@@ -3029,7 +3032,7 @@
         <v>193</v>
       </c>
       <c r="B193">
-        <v>1886.60988</v>
+        <v>1886.614489</v>
       </c>
     </row>
     <row r="194" spans="1:2">
@@ -3037,7 +3040,7 @@
         <v>194</v>
       </c>
       <c r="B194">
-        <v>1827.720368</v>
+        <v>1827.714221</v>
       </c>
     </row>
     <row r="195" spans="1:2">
@@ -3045,7 +3048,7 @@
         <v>195</v>
       </c>
       <c r="B195">
-        <v>1894.776145</v>
+        <v>1894.775663</v>
       </c>
     </row>
     <row r="196" spans="1:2">
@@ -3053,7 +3056,7 @@
         <v>196</v>
       </c>
       <c r="B196">
-        <v>1905.010904</v>
+        <v>1905.018315</v>
       </c>
     </row>
     <row r="197" spans="1:2">
@@ -3061,7 +3064,7 @@
         <v>197</v>
       </c>
       <c r="B197">
-        <v>1899.36841</v>
+        <v>1899.36228</v>
       </c>
     </row>
     <row r="198" spans="1:2">
@@ -3069,7 +3072,7 @@
         <v>198</v>
       </c>
       <c r="B198">
-        <v>1937.188042</v>
+        <v>1937.177524</v>
       </c>
     </row>
     <row r="199" spans="1:2">
@@ -3077,7 +3080,7 @@
         <v>199</v>
       </c>
       <c r="B199">
-        <v>1914.670145</v>
+        <v>1914.676054</v>
       </c>
     </row>
     <row r="200" spans="1:2">
@@ -3085,7 +3088,7 @@
         <v>200</v>
       </c>
       <c r="B200">
-        <v>1946.148886</v>
+        <v>1946.143473</v>
       </c>
     </row>
     <row r="201" spans="1:2">
@@ -3093,7 +3096,7 @@
         <v>201</v>
       </c>
       <c r="B201">
-        <v>2064.976339</v>
+        <v>2064.986159</v>
       </c>
     </row>
     <row r="202" spans="1:2">
@@ -3101,7 +3104,7 @@
         <v>202</v>
       </c>
       <c r="B202">
-        <v>2164.019106</v>
+        <v>2164.008928</v>
       </c>
     </row>
     <row r="203" spans="1:2">
@@ -3109,7 +3112,7 @@
         <v>203</v>
       </c>
       <c r="B203">
-        <v>2020.146549</v>
+        <v>2020.150739</v>
       </c>
     </row>
     <row r="204" spans="1:2">
@@ -3117,7 +3120,7 @@
         <v>204</v>
       </c>
       <c r="B204">
-        <v>2019.716016</v>
+        <v>2019.722178</v>
       </c>
     </row>
     <row r="205" spans="1:2">
@@ -3125,7 +3128,7 @@
         <v>205</v>
       </c>
       <c r="B205">
-        <v>1961.573208</v>
+        <v>1961.573295</v>
       </c>
     </row>
     <row r="206" spans="1:2">
@@ -3133,7 +3136,7 @@
         <v>206</v>
       </c>
       <c r="B206">
-        <v>1924.818093</v>
+        <v>1924.816077</v>
       </c>
     </row>
     <row r="207" spans="1:2">
@@ -3141,7 +3144,7 @@
         <v>207</v>
       </c>
       <c r="B207">
-        <v>1971.092575</v>
+        <v>1971.095069</v>
       </c>
     </row>
     <row r="208" spans="1:2">
@@ -3149,7 +3152,7 @@
         <v>208</v>
       </c>
       <c r="B208">
-        <v>1966.241915</v>
+        <v>1966.244583</v>
       </c>
     </row>
     <row r="209" spans="1:2">
@@ -3157,7 +3160,7 @@
         <v>209</v>
       </c>
       <c r="B209">
-        <v>2053.705122</v>
+        <v>2053.698457</v>
       </c>
     </row>
     <row r="210" spans="1:2">
@@ -3165,7 +3168,7 @@
         <v>210</v>
       </c>
       <c r="B210">
-        <v>2097.243598</v>
+        <v>2097.244028</v>
       </c>
     </row>
     <row r="211" spans="1:2">
@@ -3173,7 +3176,7 @@
         <v>211</v>
       </c>
       <c r="B211">
-        <v>2016.819173</v>
+        <v>2016.819401</v>
       </c>
     </row>
     <row r="212" spans="1:2">
@@ -3181,7 +3184,7 @@
         <v>212</v>
       </c>
       <c r="B212">
-        <v>1893.124347</v>
+        <v>1893.125845</v>
       </c>
     </row>
     <row r="213" spans="1:2">
@@ -3189,7 +3192,7 @@
         <v>213</v>
       </c>
       <c r="B213">
-        <v>1845.632939</v>
+        <v>1845.639201</v>
       </c>
     </row>
     <row r="214" spans="1:2">
@@ -3197,7 +3200,7 @@
         <v>214</v>
       </c>
       <c r="B214">
-        <v>1791.436799</v>
+        <v>1791.4181</v>
       </c>
     </row>
     <row r="215" spans="1:2">
@@ -3205,7 +3208,7 @@
         <v>215</v>
       </c>
       <c r="B215">
-        <v>1848.499435</v>
+        <v>1848.508468</v>
       </c>
     </row>
     <row r="216" spans="1:2">
@@ -3213,7 +3216,7 @@
         <v>216</v>
       </c>
       <c r="B216">
-        <v>1918.733348</v>
+        <v>1918.740833</v>
       </c>
     </row>
     <row r="217" spans="1:2">
@@ -3221,7 +3224,7 @@
         <v>217</v>
       </c>
       <c r="B217">
-        <v>1873.235743</v>
+        <v>1873.231183</v>
       </c>
     </row>
     <row r="218" spans="1:2">
@@ -3229,7 +3232,7 @@
         <v>218</v>
       </c>
       <c r="B218">
-        <v>1909.095028</v>
+        <v>1909.094742</v>
       </c>
     </row>
     <row r="219" spans="1:2">
@@ -3237,7 +3240,7 @@
         <v>219</v>
       </c>
       <c r="B219">
-        <v>1895.303911</v>
+        <v>1895.305178</v>
       </c>
     </row>
     <row r="220" spans="1:2">
@@ -3245,7 +3248,7 @@
         <v>220</v>
       </c>
       <c r="B220">
-        <v>1851.593021</v>
+        <v>1851.581444</v>
       </c>
     </row>
     <row r="221" spans="1:2">
@@ -3253,7 +3256,7 @@
         <v>221</v>
       </c>
       <c r="B221">
-        <v>1914.413069</v>
+        <v>1914.423319</v>
       </c>
     </row>
     <row r="222" spans="1:2">
@@ -3261,7 +3264,7 @@
         <v>222</v>
       </c>
       <c r="B222">
-        <v>1895.958321</v>
+        <v>1895.962809</v>
       </c>
     </row>
     <row r="223" spans="1:2">
@@ -3269,7 +3272,7 @@
         <v>223</v>
       </c>
       <c r="B223">
-        <v>1954.513364</v>
+        <v>1954.506783</v>
       </c>
     </row>
     <row r="224" spans="1:2">
@@ -3277,7 +3280,7 @@
         <v>224</v>
       </c>
       <c r="B224">
-        <v>1893.447546</v>
+        <v>1893.454895</v>
       </c>
     </row>
     <row r="225" spans="1:2">
@@ -3285,7 +3288,7 @@
         <v>225</v>
       </c>
       <c r="B225">
-        <v>1943.186555</v>
+        <v>1943.182714</v>
       </c>
     </row>
     <row r="226" spans="1:2">
@@ -3293,7 +3296,7 @@
         <v>226</v>
       </c>
       <c r="B226">
-        <v>1934.930266</v>
+        <v>1934.919421</v>
       </c>
     </row>
     <row r="227" spans="1:2">
@@ -3301,7 +3304,7 @@
         <v>227</v>
       </c>
       <c r="B227">
-        <v>1968.639528</v>
+        <v>1968.64764</v>
       </c>
     </row>
     <row r="228" spans="1:2">
@@ -3309,7 +3312,7 @@
         <v>228</v>
       </c>
       <c r="B228">
-        <v>1970.303314</v>
+        <v>1970.305141</v>
       </c>
     </row>
     <row r="229" spans="1:2">
@@ -3317,7 +3320,7 @@
         <v>229</v>
       </c>
       <c r="B229">
-        <v>1971.175867</v>
+        <v>1971.178603</v>
       </c>
     </row>
     <row r="230" spans="1:2">
@@ -3325,7 +3328,7 @@
         <v>230</v>
       </c>
       <c r="B230">
-        <v>2000.576328</v>
+        <v>2000.570645</v>
       </c>
     </row>
     <row r="231" spans="1:2">
@@ -3333,7 +3336,7 @@
         <v>231</v>
       </c>
       <c r="B231">
-        <v>1963.541947</v>
+        <v>1963.543804</v>
       </c>
     </row>
     <row r="232" spans="1:2">
@@ -3341,7 +3344,7 @@
         <v>232</v>
       </c>
       <c r="B232">
-        <v>2023.888811</v>
+        <v>2023.888237</v>
       </c>
     </row>
     <row r="233" spans="1:2">
@@ -3349,7 +3352,7 @@
         <v>233</v>
       </c>
       <c r="B233">
-        <v>2014.596448</v>
+        <v>2014.596441</v>
       </c>
     </row>
     <row r="234" spans="1:2">
@@ -3357,7 +3360,7 @@
         <v>234</v>
       </c>
       <c r="B234">
-        <v>1989.433384</v>
+        <v>1989.43433</v>
       </c>
     </row>
     <row r="235" spans="1:2">
@@ -3365,7 +3368,7 @@
         <v>235</v>
       </c>
       <c r="B235">
-        <v>1978.296244</v>
+        <v>1978.295858</v>
       </c>
     </row>
     <row r="236" spans="1:2">
@@ -3373,7 +3376,7 @@
         <v>236</v>
       </c>
       <c r="B236">
-        <v>1985.960243</v>
+        <v>1985.967256</v>
       </c>
     </row>
     <row r="237" spans="1:2">
@@ -3381,7 +3384,7 @@
         <v>237</v>
       </c>
       <c r="B237">
-        <v>2016.880159</v>
+        <v>2016.865065</v>
       </c>
     </row>
     <row r="238" spans="1:2">
@@ -3389,7 +3392,7 @@
         <v>238</v>
       </c>
       <c r="B238">
-        <v>2035.843264</v>
+        <v>2035.844916</v>
       </c>
     </row>
     <row r="239" spans="1:2">
@@ -3397,7 +3400,7 @@
         <v>239</v>
       </c>
       <c r="B239">
-        <v>2077.170906</v>
+        <v>2077.177577</v>
       </c>
     </row>
     <row r="240" spans="1:2">
@@ -3405,7 +3408,7 @@
         <v>240</v>
       </c>
       <c r="B240">
-        <v>2019.368042</v>
+        <v>2019.363324</v>
       </c>
     </row>
     <row r="241" spans="1:2">
@@ -3413,7 +3416,7 @@
         <v>241</v>
       </c>
       <c r="B241">
-        <v>2285.028417</v>
+        <v>2285.039707</v>
       </c>
     </row>
     <row r="242" spans="1:2">
@@ -3421,7 +3424,7 @@
         <v>242</v>
       </c>
       <c r="B242">
-        <v>1941.447934</v>
+        <v>1941.433082</v>
       </c>
     </row>
     <row r="243" spans="1:2">
@@ -3429,7 +3432,7 @@
         <v>243</v>
       </c>
       <c r="B243">
-        <v>2087.853853</v>
+        <v>2087.856083</v>
       </c>
     </row>
     <row r="244" spans="1:2">
@@ -3437,7 +3440,7 @@
         <v>244</v>
       </c>
       <c r="B244">
-        <v>2134.502801</v>
+        <v>2134.50983</v>
       </c>
     </row>
     <row r="245" spans="1:2">
@@ -3445,7 +3448,7 @@
         <v>245</v>
       </c>
       <c r="B245">
-        <v>2032.118388</v>
+        <v>2032.119478</v>
       </c>
     </row>
     <row r="246" spans="1:2">
@@ -3453,7 +3456,7 @@
         <v>246</v>
       </c>
       <c r="B246">
-        <v>2036.002155</v>
+        <v>2035.995613</v>
       </c>
     </row>
     <row r="247" spans="1:2">
@@ -3461,7 +3464,7 @@
         <v>247</v>
       </c>
       <c r="B247">
-        <v>2073.040219</v>
+        <v>2073.045914</v>
       </c>
     </row>
     <row r="248" spans="1:2">
@@ -3469,7 +3472,7 @@
         <v>248</v>
       </c>
       <c r="B248">
-        <v>2202.112085</v>
+        <v>2202.120365</v>
       </c>
     </row>
     <row r="249" spans="1:2">
@@ -3477,7 +3480,7 @@
         <v>249</v>
       </c>
       <c r="B249">
-        <v>2278.272388</v>
+        <v>2278.253827</v>
       </c>
     </row>
     <row r="250" spans="1:2">
@@ -3485,7 +3488,7 @@
         <v>250</v>
       </c>
       <c r="B250">
-        <v>2111.176261</v>
+        <v>2111.182934</v>
       </c>
     </row>
     <row r="251" spans="1:2">
@@ -3493,7 +3496,7 @@
         <v>251</v>
       </c>
       <c r="B251">
-        <v>2110.969101</v>
+        <v>2110.966745</v>
       </c>
     </row>
     <row r="252" spans="1:2">
@@ -3501,7 +3504,7 @@
         <v>252</v>
       </c>
       <c r="B252">
-        <v>2120.227828</v>
+        <v>2120.230445</v>
       </c>
     </row>
     <row r="253" spans="1:2">
@@ -3509,7 +3512,7 @@
         <v>253</v>
       </c>
       <c r="B253">
-        <v>2196.378916</v>
+        <v>2196.389735</v>
       </c>
     </row>
     <row r="254" spans="1:2">
@@ -3517,7 +3520,7 @@
         <v>254</v>
       </c>
       <c r="B254">
-        <v>2297.810367</v>
+        <v>2297.784298</v>
       </c>
     </row>
     <row r="255" spans="1:2">
@@ -3525,7 +3528,7 @@
         <v>255</v>
       </c>
       <c r="B255">
-        <v>2278.07519</v>
+        <v>2278.079675</v>
       </c>
     </row>
     <row r="256" spans="1:2">
@@ -3533,7 +3536,7 @@
         <v>256</v>
       </c>
       <c r="B256">
-        <v>2147.088414</v>
+        <v>2147.090039</v>
       </c>
     </row>
     <row r="257" spans="1:2">
@@ -3541,7 +3544,7 @@
         <v>257</v>
       </c>
       <c r="B257">
-        <v>2166.366426</v>
+        <v>2166.373224</v>
       </c>
     </row>
     <row r="258" spans="1:2">
@@ -3549,7 +3552,7 @@
         <v>258</v>
       </c>
       <c r="B258">
-        <v>2285.593074</v>
+        <v>2285.592706</v>
       </c>
     </row>
     <row r="259" spans="1:2">
@@ -3557,7 +3560,7 @@
         <v>259</v>
       </c>
       <c r="B259">
-        <v>2248.185814</v>
+        <v>2248.191087</v>
       </c>
     </row>
     <row r="260" spans="1:2">
@@ -3565,7 +3568,7 @@
         <v>260</v>
       </c>
       <c r="B260">
-        <v>2247.371931</v>
+        <v>2247.365085</v>
       </c>
     </row>
     <row r="261" spans="1:2">
@@ -3573,7 +3576,7 @@
         <v>261</v>
       </c>
       <c r="B261">
-        <v>2236.106686</v>
+        <v>2236.103738</v>
       </c>
     </row>
     <row r="262" spans="1:2">
@@ -3581,7 +3584,7 @@
         <v>262</v>
       </c>
       <c r="B262">
-        <v>2446.134664</v>
+        <v>2446.146809</v>
       </c>
     </row>
     <row r="263" spans="1:2">
@@ -3589,7 +3592,7 @@
         <v>263</v>
       </c>
       <c r="B263">
-        <v>2251.098715</v>
+        <v>2251.086779</v>
       </c>
     </row>
     <row r="264" spans="1:2">
@@ -3597,7 +3600,7 @@
         <v>264</v>
       </c>
       <c r="B264">
-        <v>2620.91264</v>
+        <v>2620.924097</v>
       </c>
     </row>
     <row r="265" spans="1:2">
@@ -3605,7 +3608,7 @@
         <v>265</v>
       </c>
       <c r="B265">
-        <v>2344.244659</v>
+        <v>2344.247811</v>
       </c>
     </row>
     <row r="266" spans="1:2">
@@ -3613,7 +3616,7 @@
         <v>266</v>
       </c>
       <c r="B266">
-        <v>2527.900607</v>
+        <v>2527.882847</v>
       </c>
     </row>
     <row r="267" spans="1:2">
@@ -3621,7 +3624,7 @@
         <v>267</v>
       </c>
       <c r="B267">
-        <v>2478.412699</v>
+        <v>2478.41477</v>
       </c>
     </row>
     <row r="268" spans="1:2">
@@ -3629,7 +3632,7 @@
         <v>268</v>
       </c>
       <c r="B268">
-        <v>2518.756852</v>
+        <v>2518.771126</v>
       </c>
     </row>
     <row r="269" spans="1:2">
@@ -3637,7 +3640,7 @@
         <v>269</v>
       </c>
       <c r="B269">
-        <v>2532.616326</v>
+        <v>2532.601602</v>
       </c>
     </row>
     <row r="270" spans="1:2">
@@ -3645,7 +3648,7 @@
         <v>270</v>
       </c>
       <c r="B270">
-        <v>2464.57133</v>
+        <v>2464.578681</v>
       </c>
     </row>
     <row r="271" spans="1:2">
@@ -3653,7 +3656,7 @@
         <v>271</v>
       </c>
       <c r="B271">
-        <v>2475.730618</v>
+        <v>2475.735533</v>
       </c>
     </row>
     <row r="272" spans="1:2">
@@ -3661,7 +3664,7 @@
         <v>272</v>
       </c>
       <c r="B272">
-        <v>2583.590124</v>
+        <v>2583.582205</v>
       </c>
     </row>
     <row r="273" spans="1:2">
@@ -3669,7 +3672,7 @@
         <v>273</v>
       </c>
       <c r="B273">
-        <v>2573.398322</v>
+        <v>2573.398598</v>
       </c>
     </row>
     <row r="274" spans="1:2">
@@ -3677,7 +3680,7 @@
         <v>274</v>
       </c>
       <c r="B274">
-        <v>2564.080201</v>
+        <v>2564.084016</v>
       </c>
     </row>
     <row r="275" spans="1:2">
@@ -3685,7 +3688,7 @@
         <v>275</v>
       </c>
       <c r="B275">
-        <v>2793.267545</v>
+        <v>2793.2614</v>
       </c>
     </row>
     <row r="276" spans="1:2">
@@ -3693,7 +3696,7 @@
         <v>276</v>
       </c>
       <c r="B276">
-        <v>2624.863975</v>
+        <v>2624.873735</v>
       </c>
     </row>
     <row r="277" spans="1:2">
@@ -3701,7 +3704,7 @@
         <v>277</v>
       </c>
       <c r="B277">
-        <v>2782.409873</v>
+        <v>2782.402226</v>
       </c>
     </row>
     <row r="278" spans="1:2">
@@ -3709,7 +3712,7 @@
         <v>278</v>
       </c>
       <c r="B278">
-        <v>2637.127361</v>
+        <v>2637.12335</v>
       </c>
     </row>
     <row r="279" spans="1:2">
@@ -3717,7 +3720,7 @@
         <v>279</v>
       </c>
       <c r="B279">
-        <v>2641.152164</v>
+        <v>2641.153756</v>
       </c>
     </row>
     <row r="280" spans="1:2">
@@ -3725,7 +3728,7 @@
         <v>280</v>
       </c>
       <c r="B280">
-        <v>2730.175045</v>
+        <v>2730.164106</v>
       </c>
     </row>
     <row r="281" spans="1:2">
@@ -3733,7 +3736,7 @@
         <v>281</v>
       </c>
       <c r="B281">
-        <v>2783.32611</v>
+        <v>2783.335049</v>
       </c>
     </row>
     <row r="282" spans="1:2">
@@ -3741,7 +3744,7 @@
         <v>282</v>
       </c>
       <c r="B282">
-        <v>2904.661054</v>
+        <v>2904.669418</v>
       </c>
     </row>
     <row r="283" spans="1:2">
@@ -3749,7 +3752,7 @@
         <v>283</v>
       </c>
       <c r="B283">
-        <v>3079.442109</v>
+        <v>3079.437188</v>
       </c>
     </row>
     <row r="284" spans="1:2">
@@ -3757,7 +3760,7 @@
         <v>284</v>
       </c>
       <c r="B284">
-        <v>2802.002549</v>
+        <v>2802.00196</v>
       </c>
     </row>
     <row r="285" spans="1:2">
@@ -3765,7 +3768,7 @@
         <v>285</v>
       </c>
       <c r="B285">
-        <v>2819.440247</v>
+        <v>2819.445575</v>
       </c>
     </row>
     <row r="286" spans="1:2">
@@ -3773,7 +3776,7 @@
         <v>286</v>
       </c>
       <c r="B286">
-        <v>2833.444514</v>
+        <v>2833.436886</v>
       </c>
     </row>
     <row r="287" spans="1:2">
@@ -3781,7 +3784,7 @@
         <v>287</v>
       </c>
       <c r="B287">
-        <v>2972.106602</v>
+        <v>2972.111475</v>
       </c>
     </row>
     <row r="288" spans="1:2">
@@ -3789,7 +3792,7 @@
         <v>288</v>
       </c>
       <c r="B288">
-        <v>3153.265912</v>
+        <v>3153.275261</v>
       </c>
     </row>
     <row r="289" spans="1:2">
@@ -3797,7 +3800,7 @@
         <v>289</v>
       </c>
       <c r="B289">
-        <v>2976.552632</v>
+        <v>2976.545075</v>
       </c>
     </row>
     <row r="290" spans="1:2">
@@ -3805,7 +3808,7 @@
         <v>290</v>
       </c>
       <c r="B290">
-        <v>2905.67193</v>
+        <v>2905.67461</v>
       </c>
     </row>
     <row r="291" spans="1:2">
@@ -3813,7 +3816,7 @@
         <v>291</v>
       </c>
       <c r="B291">
-        <v>2940.633038</v>
+        <v>2940.63117</v>
       </c>
     </row>
     <row r="292" spans="1:2">
@@ -3821,7 +3824,7 @@
         <v>292</v>
       </c>
       <c r="B292">
-        <v>2998.557675</v>
+        <v>2998.544599</v>
       </c>
     </row>
     <row r="293" spans="1:2">
@@ -3829,7 +3832,7 @@
         <v>293</v>
       </c>
       <c r="B293">
-        <v>3054.376215</v>
+        <v>3054.375131</v>
       </c>
     </row>
     <row r="294" spans="1:2">
@@ -3837,7 +3840,7 @@
         <v>294</v>
       </c>
       <c r="B294">
-        <v>3052.003705</v>
+        <v>3052.012294</v>
       </c>
     </row>
     <row r="295" spans="1:2">
@@ -3845,7 +3848,7 @@
         <v>295</v>
       </c>
       <c r="B295">
-        <v>3164.092751</v>
+        <v>3164.077707</v>
       </c>
     </row>
     <row r="296" spans="1:2">
@@ -3853,7 +3856,7 @@
         <v>296</v>
       </c>
       <c r="B296">
-        <v>3179.216281</v>
+        <v>3179.229655</v>
       </c>
     </row>
     <row r="297" spans="1:2">
@@ -3861,7 +3864,7 @@
         <v>297</v>
       </c>
       <c r="B297">
-        <v>3334.988306</v>
+        <v>3334.993284</v>
       </c>
     </row>
     <row r="298" spans="1:2">
@@ -3869,7 +3872,7 @@
         <v>298</v>
       </c>
       <c r="B298">
-        <v>3183.508126</v>
+        <v>3183.511421</v>
       </c>
     </row>
     <row r="299" spans="1:2">
@@ -3877,7 +3880,7 @@
         <v>299</v>
       </c>
       <c r="B299">
-        <v>3061.566531</v>
+        <v>3061.576737</v>
       </c>
     </row>
     <row r="300" spans="1:2">
@@ -3885,7 +3888,7 @@
         <v>300</v>
       </c>
       <c r="B300">
-        <v>3160.789506</v>
+        <v>3160.787362</v>
       </c>
     </row>
     <row r="301" spans="1:2">
@@ -3893,7 +3896,7 @@
         <v>301</v>
       </c>
       <c r="B301">
-        <v>3124.471107</v>
+        <v>3124.474937</v>
       </c>
     </row>
     <row r="302" spans="1:2">
@@ -3901,7 +3904,7 @@
         <v>302</v>
       </c>
       <c r="B302">
-        <v>3090.984642</v>
+        <v>3090.98969</v>
       </c>
     </row>
     <row r="303" spans="1:2">
@@ -3909,7 +3912,7 @@
         <v>303</v>
       </c>
       <c r="B303">
-        <v>3244.864016</v>
+        <v>3244.840418</v>
       </c>
     </row>
     <row r="304" spans="1:2">
@@ -3917,7 +3920,7 @@
         <v>304</v>
       </c>
       <c r="B304">
-        <v>4086.725475</v>
+        <v>4086.697204</v>
       </c>
     </row>
     <row r="305" spans="1:2">
@@ -3925,7 +3928,7 @@
         <v>305</v>
       </c>
       <c r="B305">
-        <v>3018.980766</v>
+        <v>3018.969548</v>
       </c>
     </row>
     <row r="306" spans="1:2">
@@ -3933,7 +3936,7 @@
         <v>306</v>
       </c>
       <c r="B306">
-        <v>3282.107718</v>
+        <v>3282.093687</v>
       </c>
     </row>
     <row r="307" spans="1:2">
@@ -3941,7 +3944,7 @@
         <v>307</v>
       </c>
       <c r="B307">
-        <v>3409.403785</v>
+        <v>3409.424835</v>
       </c>
     </row>
     <row r="308" spans="1:2">
@@ -3949,7 +3952,7 @@
         <v>308</v>
       </c>
       <c r="B308">
-        <v>3397.091708</v>
+        <v>3397.130921</v>
       </c>
     </row>
     <row r="309" spans="1:2">
@@ -3957,7 +3960,7 @@
         <v>309</v>
       </c>
       <c r="B309">
-        <v>3514.285519</v>
+        <v>3514.305721</v>
       </c>
     </row>
     <row r="310" spans="1:2">
@@ -3965,7 +3968,7 @@
         <v>310</v>
       </c>
       <c r="B310">
-        <v>3639.122481</v>
+        <v>3639.084282</v>
       </c>
     </row>
     <row r="311" spans="1:2">
@@ -3973,7 +3976,7 @@
         <v>311</v>
       </c>
       <c r="B311">
-        <v>3521.454255</v>
+        <v>3521.462649</v>
       </c>
     </row>
     <row r="312" spans="1:2">
@@ -3981,7 +3984,7 @@
         <v>312</v>
       </c>
       <c r="B312">
-        <v>3646.845912</v>
+        <v>3646.829858</v>
       </c>
     </row>
     <row r="313" spans="1:2">
@@ -3989,7 +3992,7 @@
         <v>313</v>
       </c>
       <c r="B313">
-        <v>3631.714139</v>
+        <v>3631.74874</v>
       </c>
     </row>
     <row r="314" spans="1:2">
@@ -3997,7 +4000,7 @@
         <v>314</v>
       </c>
       <c r="B314">
-        <v>4012.031498</v>
+        <v>4012.0298</v>
       </c>
     </row>
     <row r="315" spans="1:2">
@@ -4005,7 +4008,7 @@
         <v>315</v>
       </c>
       <c r="B315">
-        <v>3908.544565</v>
+        <v>3908.551832</v>
       </c>
     </row>
     <row r="316" spans="1:2">
@@ -4013,7 +4016,7 @@
         <v>316</v>
       </c>
       <c r="B316">
-        <v>4211.56522</v>
+        <v>4211.59717</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -4021,7 +4024,7 @@
         <v>317</v>
       </c>
       <c r="B317">
-        <v>4223.905408</v>
+        <v>4223.930388</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -4029,7 +4032,7 @@
         <v>318</v>
       </c>
       <c r="B318">
-        <v>4365.567572</v>
+        <v>4365.15546</v>
       </c>
     </row>
     <row r="319" spans="1:2">
@@ -4037,7 +4040,7 @@
         <v>319</v>
       </c>
       <c r="B319">
-        <v>4325.591997</v>
+        <v>4325.679319</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -4045,7 +4048,7 @@
         <v>320</v>
       </c>
       <c r="B320">
-        <v>4340.018414</v>
+        <v>4340.558451</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -4053,7 +4056,7 @@
         <v>321</v>
       </c>
       <c r="B321">
-        <v>4528.096257</v>
+        <v>4527.996393</v>
       </c>
     </row>
     <row r="322" spans="1:2">
@@ -4061,7 +4064,7 @@
         <v>322</v>
       </c>
       <c r="B322">
-        <v>4387.740081</v>
+        <v>4387.493637</v>
       </c>
     </row>
     <row r="323" spans="1:2">
@@ -4069,7 +4072,7 @@
         <v>323</v>
       </c>
       <c r="B323">
-        <v>4626.671765</v>
+        <v>4626.578298</v>
       </c>
     </row>
     <row r="324" spans="1:2">
@@ -4077,7 +4080,7 @@
         <v>324</v>
       </c>
       <c r="B324">
-        <v>4819.77521</v>
+        <v>4819.72282</v>
       </c>
     </row>
     <row r="325" spans="1:2">
@@ -4085,7 +4088,7 @@
         <v>325</v>
       </c>
       <c r="B325">
-        <v>4619.929995</v>
+        <v>4619.990786</v>
       </c>
     </row>
     <row r="326" spans="1:2">
@@ -4093,7 +4096,7 @@
         <v>326</v>
       </c>
       <c r="B326">
-        <v>4628.959257</v>
+        <v>4629.046657</v>
       </c>
     </row>
     <row r="327" spans="1:2">
@@ -4101,7 +4104,7 @@
         <v>327</v>
       </c>
       <c r="B327">
-        <v>4713.862487</v>
+        <v>4714.022103</v>
       </c>
     </row>
     <row r="328" spans="1:2">
@@ -4109,7 +4112,7 @@
         <v>328</v>
       </c>
       <c r="B328">
-        <v>4663.795624</v>
+        <v>4664.009142</v>
       </c>
     </row>
     <row r="329" spans="1:2">
@@ -4117,7 +4120,7 @@
         <v>329</v>
       </c>
       <c r="B329">
-        <v>4888.021545</v>
+        <v>4888.180258</v>
       </c>
     </row>
     <row r="330" spans="1:2">
@@ -4125,7 +4128,7 @@
         <v>330</v>
       </c>
       <c r="B330">
-        <v>4817.303431</v>
+        <v>4816.463484</v>
       </c>
     </row>
     <row r="331" spans="1:2">
@@ -4133,7 +4136,7 @@
         <v>331</v>
       </c>
       <c r="B331">
-        <v>4860.414548</v>
+        <v>4860.551923</v>
       </c>
     </row>
     <row r="332" spans="1:2">
@@ -4141,7 +4144,7 @@
         <v>332</v>
       </c>
       <c r="B332">
-        <v>5062.77017</v>
+        <v>5063.860974</v>
       </c>
     </row>
     <row r="333" spans="1:2">
@@ -4149,7 +4152,7 @@
         <v>333</v>
       </c>
       <c r="B333">
-        <v>4809.626874</v>
+        <v>4809.234592</v>
       </c>
     </row>
     <row r="334" spans="1:2">
@@ -4157,7 +4160,7 @@
         <v>334</v>
       </c>
       <c r="B334">
-        <v>5033.900014</v>
+        <v>5033.226703</v>
       </c>
     </row>
     <row r="335" spans="1:2">
@@ -4165,7 +4168,7 @@
         <v>335</v>
       </c>
       <c r="B335">
-        <v>5117.34619</v>
+        <v>5117.018343</v>
       </c>
     </row>
     <row r="336" spans="1:2">
@@ -4173,7 +4176,7 @@
         <v>336</v>
       </c>
       <c r="B336">
-        <v>4955.201984</v>
+        <v>4955.055448</v>
       </c>
     </row>
     <row r="337" spans="1:2">
@@ -4181,7 +4184,7 @@
         <v>337</v>
       </c>
       <c r="B337">
-        <v>5270.36822</v>
+        <v>5270.446389</v>
       </c>
     </row>
     <row r="338" spans="1:2">
@@ -4189,7 +4192,7 @@
         <v>338</v>
       </c>
       <c r="B338">
-        <v>5142.589258</v>
+        <v>5142.904534</v>
       </c>
     </row>
     <row r="339" spans="1:2">
@@ -4197,7 +4200,7 @@
         <v>339</v>
       </c>
       <c r="B339">
-        <v>5208.213711</v>
+        <v>5208.811684</v>
       </c>
     </row>
     <row r="340" spans="1:2">
@@ -4205,7 +4208,7 @@
         <v>340</v>
       </c>
       <c r="B340">
-        <v>5144.243425</v>
+        <v>5145.061585</v>
       </c>
     </row>
     <row r="341" spans="1:2">
@@ -4213,7 +4216,7 @@
         <v>341</v>
       </c>
       <c r="B341">
-        <v>5251.349342</v>
+        <v>5251.862018</v>
       </c>
     </row>
     <row r="342" spans="1:2">
@@ -4221,7 +4224,7 @@
         <v>342</v>
       </c>
       <c r="B342">
-        <v>5261.913334</v>
+        <v>5260.542014</v>
       </c>
     </row>
     <row r="343" spans="1:2">
@@ -4229,7 +4232,7 @@
         <v>343</v>
       </c>
       <c r="B343">
-        <v>5299.64587</v>
+        <v>5300.950101</v>
       </c>
     </row>
     <row r="344" spans="1:2">
@@ -4237,7 +4240,7 @@
         <v>344</v>
       </c>
       <c r="B344">
-        <v>5377.348556</v>
+        <v>5377.35728</v>
       </c>
     </row>
     <row r="345" spans="1:2">
@@ -4245,7 +4248,7 @@
         <v>345</v>
       </c>
       <c r="B345">
-        <v>5158.225206</v>
+        <v>5157.109895</v>
       </c>
     </row>
     <row r="346" spans="1:2">
@@ -4253,7 +4256,7 @@
         <v>346</v>
       </c>
       <c r="B346">
-        <v>5629.943461</v>
+        <v>5628.854708</v>
       </c>
     </row>
     <row r="347" spans="1:2">
@@ -4261,7 +4264,7 @@
         <v>347</v>
       </c>
       <c r="B347">
-        <v>5422.233642</v>
+        <v>5421.723035</v>
       </c>
     </row>
     <row r="348" spans="1:2">
@@ -4269,7 +4272,7 @@
         <v>348</v>
       </c>
       <c r="B348">
-        <v>4989.132383</v>
+        <v>4988.975061</v>
       </c>
     </row>
     <row r="349" spans="1:2">
@@ -4277,7 +4280,7 @@
         <v>349</v>
       </c>
       <c r="B349">
-        <v>5446.410456</v>
+        <v>5446.630229</v>
       </c>
     </row>
     <row r="350" spans="1:2">
@@ -4285,7 +4288,7 @@
         <v>350</v>
       </c>
       <c r="B350">
-        <v>5237.235865</v>
+        <v>5237.654536</v>
       </c>
     </row>
     <row r="351" spans="1:2">
@@ -4293,7 +4296,7 @@
         <v>351</v>
       </c>
       <c r="B351">
-        <v>5178.049427</v>
+        <v>5178.639446</v>
       </c>
     </row>
     <row r="352" spans="1:2">
@@ -4301,7 +4304,7 @@
         <v>352</v>
       </c>
       <c r="B352">
-        <v>5270.432121</v>
+        <v>5271.335973</v>
       </c>
     </row>
     <row r="353" spans="1:2">
@@ -4309,7 +4312,7 @@
         <v>353</v>
       </c>
       <c r="B353">
-        <v>5436.942727</v>
+        <v>5437.161192</v>
       </c>
     </row>
     <row r="354" spans="1:2">
@@ -4317,7 +4320,7 @@
         <v>354</v>
       </c>
       <c r="B354">
-        <v>5251.050809</v>
+        <v>5248.438133</v>
       </c>
     </row>
     <row r="355" spans="1:2">
@@ -4325,7 +4328,7 @@
         <v>355</v>
       </c>
       <c r="B355">
-        <v>6065.563965</v>
+        <v>6066.664854</v>
       </c>
     </row>
     <row r="356" spans="1:2">
@@ -4333,7 +4336,7 @@
         <v>356</v>
       </c>
       <c r="B356">
-        <v>5231.930563</v>
+        <v>5237.777155</v>
       </c>
     </row>
     <row r="357" spans="1:2">
@@ -4341,7 +4344,7 @@
         <v>357</v>
       </c>
       <c r="B357">
-        <v>5682.156797</v>
+        <v>5679.533556</v>
       </c>
     </row>
     <row r="358" spans="1:2">
@@ -4349,7 +4352,7 @@
         <v>358</v>
       </c>
       <c r="B358">
-        <v>5395.39192</v>
+        <v>5393.50495</v>
       </c>
     </row>
     <row r="359" spans="1:2">
@@ -4357,7 +4360,7 @@
         <v>359</v>
       </c>
       <c r="B359">
-        <v>5303.422908</v>
+        <v>5302.223985</v>
       </c>
     </row>
     <row r="360" spans="1:2">
@@ -4365,7 +4368,7 @@
         <v>360</v>
       </c>
       <c r="B360">
-        <v>5582.104087</v>
+        <v>5581.258706</v>
       </c>
     </row>
     <row r="361" spans="1:2">
@@ -4373,7 +4376,7 @@
         <v>361</v>
       </c>
       <c r="B361">
-        <v>5159.976635</v>
+        <v>5159.711513</v>
       </c>
     </row>
     <row r="362" spans="1:2">
@@ -4381,7 +4384,7 @@
         <v>362</v>
       </c>
       <c r="B362">
-        <v>5356.108395</v>
+        <v>5356.089543</v>
       </c>
     </row>
     <row r="363" spans="1:2">
@@ -4389,7 +4392,7 @@
         <v>363</v>
       </c>
       <c r="B363">
-        <v>5337.784954</v>
+        <v>5338.061422</v>
       </c>
     </row>
     <row r="364" spans="1:2">
@@ -4397,7 +4400,7 @@
         <v>364</v>
       </c>
       <c r="B364">
-        <v>5227.052708</v>
+        <v>5227.834979</v>
       </c>
     </row>
     <row r="365" spans="1:2">
@@ -4405,7 +4408,7 @@
         <v>365</v>
       </c>
       <c r="B365">
-        <v>5033.643529</v>
+        <v>5033.109672</v>
       </c>
     </row>
     <row r="366" spans="1:2">
@@ -4413,7 +4416,7 @@
         <v>366</v>
       </c>
       <c r="B366">
-        <v>5114.567189</v>
+        <v>5110.125899</v>
       </c>
     </row>
     <row r="367" spans="1:2">
@@ -4421,7 +4424,7 @@
         <v>367</v>
       </c>
       <c r="B367">
-        <v>5078.663318</v>
+        <v>5079.059117</v>
       </c>
     </row>
     <row r="368" spans="1:2">
@@ -4429,7 +4432,7 @@
         <v>368</v>
       </c>
       <c r="B368">
-        <v>5065.357767</v>
+        <v>5080.366725</v>
       </c>
     </row>
     <row r="369" spans="1:2">
@@ -4437,7 +4440,7 @@
         <v>369</v>
       </c>
       <c r="B369">
-        <v>5276.21499</v>
+        <v>5272.098751</v>
       </c>
     </row>
     <row r="370" spans="1:2">
@@ -4445,7 +4448,7 @@
         <v>370</v>
       </c>
       <c r="B370">
-        <v>5218.046372</v>
+        <v>5215.226012</v>
       </c>
     </row>
     <row r="371" spans="1:2">
@@ -4453,7 +4456,7 @@
         <v>371</v>
       </c>
       <c r="B371">
-        <v>5258.787837</v>
+        <v>5256.615065</v>
       </c>
     </row>
     <row r="372" spans="1:2">
@@ -4461,7 +4464,7 @@
         <v>372</v>
       </c>
       <c r="B372">
-        <v>5336.8436</v>
+        <v>5335.09069</v>
       </c>
     </row>
     <row r="373" spans="1:2">
@@ -4469,7 +4472,7 @@
         <v>373</v>
       </c>
       <c r="B373">
-        <v>5247.307576</v>
+        <v>5246.199606</v>
       </c>
     </row>
     <row r="374" spans="1:2">
@@ -4477,7 +4480,7 @@
         <v>374</v>
       </c>
       <c r="B374">
-        <v>5346.72359</v>
+        <v>5345.765063</v>
       </c>
     </row>
     <row r="375" spans="1:2">
@@ -4485,7 +4488,7 @@
         <v>375</v>
       </c>
       <c r="B375">
-        <v>5380.836829</v>
+        <v>5380.132678</v>
       </c>
     </row>
     <row r="376" spans="1:2">
@@ -4493,7 +4496,7 @@
         <v>376</v>
       </c>
       <c r="B376">
-        <v>5453.519095</v>
+        <v>5453.412276</v>
       </c>
     </row>
     <row r="377" spans="1:2">
@@ -4501,7 +4504,7 @@
         <v>377</v>
       </c>
       <c r="B377">
-        <v>5260.386669</v>
+        <v>5263.785747</v>
       </c>
     </row>
     <row r="378" spans="1:2">
@@ -4509,7 +4512,7 @@
         <v>378</v>
       </c>
       <c r="B378">
-        <v>5371.814375</v>
+        <v>5378.253847</v>
       </c>
     </row>
     <row r="379" spans="1:2">
@@ -4517,7 +4520,15 @@
         <v>379</v>
       </c>
       <c r="B379">
-        <v>5245.488869</v>
+        <v>5244.335941</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" t="s">
+        <v>380</v>
+      </c>
+      <c r="B380">
+        <v>5271.376062</v>
       </c>
     </row>
   </sheetData>
